--- a/data/trans_orig/P57B4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023</t>
+          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208869</t>
+          <t>209570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254805</t>
+          <t>255808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188146</t>
+          <t>188257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226179</t>
+          <t>225650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>408504</t>
+          <t>407061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>466609</t>
+          <t>467757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199324</t>
+          <t>197253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244852</t>
+          <t>242654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176247</t>
+          <t>177111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212141</t>
+          <t>214101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384235</t>
+          <t>387403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442893</t>
+          <t>445776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56298</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65261</t>
+          <t>64540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95380</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183323</t>
+          <t>181722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227236</t>
+          <t>226011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140536</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173165</t>
+          <t>174113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>337146</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>393264</t>
+          <t>392000</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>169908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213667</t>
+          <t>213953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151929</t>
+          <t>150504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184046</t>
+          <t>183765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330256</t>
+          <t>329549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384944</t>
+          <t>385151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>40254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68080</t>
+          <t>68159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41107</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87237</t>
+          <t>85671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120819</t>
+          <t>120439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288806</t>
+          <t>287011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580954</t>
+          <t>571511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47161</t>
+          <t>45601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66393</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337083</t>
+          <t>337894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688945</t>
+          <t>696445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>72086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>291329</t>
+          <t>296031</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70287</t>
+          <t>70139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90915</t>
+          <t>91412</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>105244</t>
+          <t>102363</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>378271</t>
+          <t>380265</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75820</t>
+          <t>76248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103964</t>
+          <t>102088</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>377099</t>
+          <t>375182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>450673</t>
+          <t>445889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>335039</t>
+          <t>335976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>696513</t>
+          <t>733096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>752584</t>
+          <t>746039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1233601</t>
+          <t>1225113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>411480</t>
+          <t>412588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>483466</t>
+          <t>482731</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>203169</t>
+          <t>181368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>473085</t>
+          <t>470813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561199</t>
+          <t>560358</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>918781</t>
+          <t>922420</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123050</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>166754</t>
+          <t>167713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56348</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134525</t>
+          <t>135783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170736</t>
+          <t>169848</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>283351</t>
+          <t>283014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>61516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42275</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>40250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>88525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>140789</t>
+          <t>141374</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187202</t>
+          <t>186538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>143837</t>
+          <t>150809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228818</t>
+          <t>231623</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>299006</t>
+          <t>298054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>403541</t>
+          <t>405593</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>185344</t>
+          <t>183246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>232230</t>
+          <t>229054</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>382990</t>
+          <t>386045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>543473</t>
+          <t>542054</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>586288</t>
+          <t>587609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>765807</t>
+          <t>768189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>60958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92955</t>
+          <t>93322</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118609</t>
+          <t>119730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>191708</t>
+          <t>189093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>196184</t>
+          <t>197363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>271190</t>
+          <t>270975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47453</t>
+          <t>45516</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>78210</t>
+          <t>75596</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>123029</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>172187</t>
+          <t>173785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>239688</t>
+          <t>238265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>289308</t>
+          <t>291151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>377032</t>
+          <t>377441</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>453730</t>
+          <t>452653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52850</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99115</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>317671</t>
+          <t>318645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>369309</t>
+          <t>370418</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>381820</t>
+          <t>380016</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>455538</t>
+          <t>454914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>106383</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>138999</t>
+          <t>140462</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>117429</t>
+          <t>118875</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>158448</t>
+          <t>159640</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5231</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1434335</t>
+          <t>1431981</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2015563</t>
+          <t>2070591</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1202682</t>
+          <t>1199853</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1806179</t>
+          <t>1829219</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2688186</t>
+          <t>2686118</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3478656</t>
+          <t>3424235</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1013215</t>
+          <t>968368</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1443310</t>
+          <t>1451818</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1310377</t>
+          <t>1232518</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1733787</t>
+          <t>1721171</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2528817</t>
+          <t>2552262</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3122498</t>
+          <t>3120990</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>287819</t>
+          <t>291618</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>420807</t>
+          <t>421320</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>404822</t>
+          <t>405495</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>544604</t>
+          <t>550650</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>747328</t>
+          <t>761909</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>942178</t>
+          <t>947304</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>55425</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>106102</t>
+          <t>110677</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>80760</t>
+          <t>81907</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>120195</t>
+          <t>122321</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>215008</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>231842</t>
+          <t>253702</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209570</t>
+          <t>229692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255808</t>
+          <t>279328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188257</t>
+          <t>206819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225650</t>
+          <t>245394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>438164</t>
+          <t>478739</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>407061</t>
+          <t>447616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>467757</t>
+          <t>509543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>220279</t>
+          <t>236904</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197253</t>
+          <t>211259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242654</t>
+          <t>259663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195307</t>
+          <t>211029</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177111</t>
+          <t>191061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214101</t>
+          <t>228542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>415586</t>
+          <t>447934</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>387403</t>
+          <t>419758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>445776</t>
+          <t>479707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43267</t>
+          <t>47562</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32976</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56397</t>
+          <t>63981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>40929</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45011</t>
+          <t>52664</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>78413</t>
+          <t>88491</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64540</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>108861</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>445956</t>
+          <t>486845</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445956</t>
+          <t>486845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445956</t>
+          <t>486845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>951168</t>
+          <t>1037464</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951168</t>
+          <t>1037464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951168</t>
+          <t>1037464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206222</t>
+          <t>224581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181722</t>
+          <t>201632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>226011</t>
+          <t>245991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>157006</t>
+          <t>175880</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>141458</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174113</t>
+          <t>193417</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>363228</t>
+          <t>400461</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>336352</t>
+          <t>369055</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>392000</t>
+          <t>429683</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>190677</t>
+          <t>200041</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>178403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213953</t>
+          <t>222811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>167900</t>
+          <t>181427</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150504</t>
+          <t>165922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183765</t>
+          <t>197993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>358578</t>
+          <t>381468</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329549</t>
+          <t>352470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385151</t>
+          <t>409597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>69653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>57253</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>46210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>69622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>102354</t>
+          <t>112156</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85671</t>
+          <t>95702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120439</t>
+          <t>135743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>450190</t>
+          <t>481042</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>450190</t>
+          <t>481042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>450190</t>
+          <t>481042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>380721</t>
+          <t>421381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>380721</t>
+          <t>421381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>380721</t>
+          <t>421381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>830911</t>
+          <t>902424</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>830911</t>
+          <t>902424</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>830911</t>
+          <t>902424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>433840</t>
+          <t>212134</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287011</t>
+          <t>188235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571511</t>
+          <t>233344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56111</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>74899</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>489951</t>
+          <t>276321</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337894</t>
+          <t>250679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696445</t>
+          <t>302307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>180109</t>
+          <t>201846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72086</t>
+          <t>180514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>296031</t>
+          <t>222901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80812</t>
+          <t>91059</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>79244</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91412</t>
+          <t>103421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>260921</t>
+          <t>292904</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102363</t>
+          <t>268834</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>380265</t>
+          <t>318225</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44347</t>
+          <t>46995</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76248</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32347</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30777</t>
+          <t>59315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102088</t>
+          <t>89070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14231</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834002</t>
+          <t>657904</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834002</t>
+          <t>657904</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834002</t>
+          <t>657904</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>411966</t>
+          <t>447838</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>375182</t>
+          <t>415493</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>445889</t>
+          <t>487973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>477017</t>
+          <t>302872</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>335976</t>
+          <t>275570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>733096</t>
+          <t>328122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>888983</t>
+          <t>750711</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>746039</t>
+          <t>706329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1225113</t>
+          <t>796655</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>447708</t>
+          <t>500954</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>412588</t>
+          <t>464210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>482731</t>
+          <t>535059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>365998</t>
+          <t>408764</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>381434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>470813</t>
+          <t>435497</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>813706</t>
+          <t>909718</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560358</t>
+          <t>863966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>922420</t>
+          <t>953304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>142745</t>
+          <t>156804</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122270</t>
+          <t>133939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167713</t>
+          <t>179678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102791</t>
+          <t>115437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>100608</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>131853</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>245536</t>
+          <t>272241</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169848</t>
+          <t>246278</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>283014</t>
+          <t>298591</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>41156</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58509</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>41523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88525</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1031043</t>
+          <t>1127599</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1031043</t>
+          <t>1127599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1031043</t>
+          <t>1127599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>975691</t>
+          <t>858931</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>975691</t>
+          <t>858931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>975691</t>
+          <t>858931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2006734</t>
+          <t>1986530</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2006734</t>
+          <t>1986530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2006734</t>
+          <t>1986530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>162364</t>
+          <t>186468</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141374</t>
+          <t>161233</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>186538</t>
+          <t>214491</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>224189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150809</t>
+          <t>202948</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>231623</t>
+          <t>247521</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>360707</t>
+          <t>410657</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>298054</t>
+          <t>376897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>444900</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>205699</t>
+          <t>248214</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183246</t>
+          <t>220620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229054</t>
+          <t>272416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>439582</t>
+          <t>385352</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>386045</t>
+          <t>361489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>542054</t>
+          <t>408751</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>645280</t>
+          <t>633566</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>587609</t>
+          <t>600302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>768189</t>
+          <t>667035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>76305</t>
+          <t>94074</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>76715</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93322</t>
+          <t>115511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>161388</t>
+          <t>176068</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119730</t>
+          <t>157223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189093</t>
+          <t>197193</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>237693</t>
+          <t>270142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197363</t>
+          <t>242270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>270975</t>
+          <t>299451</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>28842</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>39968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36020</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>29907</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>60733</t>
+          <t>67195</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>54964</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>75596</t>
+          <t>82916</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>469081</t>
+          <t>557598</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>469081</t>
+          <t>557598</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>469081</t>
+          <t>557598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>835333</t>
+          <t>823962</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>835333</t>
+          <t>823962</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>835333</t>
+          <t>823962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1304413</t>
+          <t>1381560</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1304413</t>
+          <t>1381560</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1304413</t>
+          <t>1381560</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>149384</t>
+          <t>154733</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>123857</t>
+          <t>132204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>173785</t>
+          <t>176118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>263869</t>
+          <t>295913</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>238265</t>
+          <t>269733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>291151</t>
+          <t>325025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>413253</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>377441</t>
+          <t>413294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>452653</t>
+          <t>486809</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97946</t>
+          <t>87365</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>343465</t>
+          <t>380317</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>318645</t>
+          <t>351819</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>370418</t>
+          <t>411086</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>417244</t>
+          <t>445983</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>380016</t>
+          <t>411928</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>454914</t>
+          <t>482043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32070</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>122100</t>
+          <t>133400</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>106383</t>
+          <t>116394</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>140462</t>
+          <t>151336</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>136841</t>
+          <t>147690</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>118875</t>
+          <t>129278</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>159640</t>
+          <t>170793</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>925</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>26530</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>238899</t>
+          <t>235614</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>238899</t>
+          <t>235614</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>238899</t>
+          <t>235614</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>746806</t>
+          <t>828521</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>746806</t>
+          <t>828521</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>746806</t>
+          <t>828521</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>985705</t>
+          <t>1064135</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>985705</t>
+          <t>1064135</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>985705</t>
+          <t>1064135</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1595618</t>
+          <t>1479456</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1431981</t>
+          <t>1414017</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2070591</t>
+          <t>1547106</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1358669</t>
+          <t>1288078</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1199853</t>
+          <t>1234465</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1829219</t>
+          <t>1348494</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2954287</t>
+          <t>2767533</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2686118</t>
+          <t>2677137</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3424235</t>
+          <t>2850544</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1318252</t>
+          <t>1453624</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>968368</t>
+          <t>1390968</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1451818</t>
+          <t>1517488</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1593062</t>
+          <t>1657947</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1232518</t>
+          <t>1599220</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1721171</t>
+          <t>1711330</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2911314</t>
+          <t>3111571</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2552262</t>
+          <t>3030628</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3120990</t>
+          <t>3197589</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>373324</t>
+          <t>414629</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>291618</t>
+          <t>378832</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>421320</t>
+          <t>457537</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>496412</t>
+          <t>549711</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>405495</t>
+          <t>514563</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>550650</t>
+          <t>586700</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>869736</t>
+          <t>964340</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>761909</t>
+          <t>910124</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>947304</t>
+          <t>1014963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>75495</t>
+          <t>76375</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>54502</t>
+          <t>60768</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>110677</t>
+          <t>94021</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>102101</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>81907</t>
+          <t>94234</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>128464</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>177596</t>
+          <t>186572</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>163652</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>211701</t>
+          <t>209665</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3362689</t>
+          <t>3424084</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3362689</t>
+          <t>3424084</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3362689</t>
+          <t>3424084</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3550244</t>
+          <t>3605933</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3550244</t>
+          <t>3605933</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3550244</t>
+          <t>3605933</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6912933</t>
+          <t>7030016</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6912933</t>
+          <t>7030016</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6912933</t>
+          <t>7030016</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
